--- a/data/trans_dic/P21_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 21,9</t>
+          <t>16,94; 21,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,16; 28,81</t>
+          <t>23,17; 28,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,81; 21,28</t>
+          <t>16,01; 21,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,24; 29,45</t>
+          <t>22,45; 30,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,73; 28,27</t>
+          <t>23,75; 28,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 33,29</t>
+          <t>28,25; 33,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,51; 25,92</t>
+          <t>20,25; 25,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,59; 31,68</t>
+          <t>26,71; 31,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,66; 30,56</t>
+          <t>26,67; 30,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 22,85</t>
+          <t>19,18; 23,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,71; 29,94</t>
+          <t>25,81; 29,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,87; 18,49</t>
+          <t>14,99; 18,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 21,66</t>
+          <t>17,74; 21,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 18,45</t>
+          <t>15,22; 18,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,48</t>
+          <t>12,15; 20,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 26,08</t>
+          <t>21,8; 25,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,68; 27,8</t>
+          <t>23,55; 27,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 21,64</t>
+          <t>18,18; 21,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 48,89</t>
+          <t>21,53; 46,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,58</t>
+          <t>18,77; 21,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,19; 24,06</t>
+          <t>21,14; 23,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,03; 19,57</t>
+          <t>17,12; 19,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 36,62</t>
+          <t>18,56; 34,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 17,97</t>
+          <t>11,51; 18,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 17,97</t>
+          <t>11,44; 17,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 17,2</t>
+          <t>10,88; 17,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 25,39</t>
+          <t>18,38; 25,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,46; 26,19</t>
+          <t>18,51; 26,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,2; 29,39</t>
+          <t>21,23; 29,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,38; 28,79</t>
+          <t>20,98; 28,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,06; 29,38</t>
+          <t>22,92; 29,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,87</t>
+          <t>15,54; 20,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,79; 22,52</t>
+          <t>16,95; 22,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 21,76</t>
+          <t>16,74; 21,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 26,13</t>
+          <t>21,47; 26,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 18,54</t>
+          <t>15,73; 18,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 22,19</t>
+          <t>19,15; 22,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,32; 17,96</t>
+          <t>15,36; 18,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 21,68</t>
+          <t>15,75; 21,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,86</t>
+          <t>22,94; 25,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 29,08</t>
+          <t>26,11; 29,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 22,95</t>
+          <t>20,14; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,06; 42,0</t>
+          <t>23,82; 41,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 21,78</t>
+          <t>19,83; 21,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 25,31</t>
+          <t>23,14; 25,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 20,03</t>
+          <t>18,11; 20,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,29; 31,78</t>
+          <t>21,28; 32,12</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>176998; 225931</t>
+          <t>174802; 224358</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>225578; 280572</t>
+          <t>225645; 278109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118941; 160105</t>
+          <t>120463; 160363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114537; 151643</t>
+          <t>115600; 154533</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>312108; 371720</t>
+          <t>312365; 377621</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>374398; 444998</t>
+          <t>377691; 444573</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>203431; 257062</t>
+          <t>200823; 254620</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>199863; 238053</t>
+          <t>200727; 238325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>500612; 581049</t>
+          <t>500576; 581056</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616095; 706207</t>
+          <t>616352; 706495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331715; 398519</t>
+          <t>334595; 401142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>325604; 379213</t>
+          <t>326866; 378685</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>251656; 312947</t>
+          <t>253785; 312891</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>351337; 424952</t>
+          <t>348086; 424969</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>310734; 381825</t>
+          <t>315050; 385356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>290135; 469064</t>
+          <t>278180; 470983</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>345914; 413788</t>
+          <t>345939; 409083</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>415672; 488003</t>
+          <t>413502; 490932</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>360371; 430024</t>
+          <t>361217; 429336</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>477557; 1092276</t>
+          <t>480976; 1041677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>611147; 707704</t>
+          <t>615404; 704252</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>787733; 894640</t>
+          <t>785830; 889402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>690766; 794046</t>
+          <t>694716; 788659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>855756; 1657051</t>
+          <t>839755; 1561513</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64144; 99105</t>
+          <t>63440; 99624</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54837; 86450</t>
+          <t>55029; 86169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58683; 93709</t>
+          <t>59305; 93465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116307; 163712</t>
+          <t>118497; 166598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87957; 124766</t>
+          <t>88194; 124769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97217; 134785</t>
+          <t>97376; 135872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116811; 157344</t>
+          <t>114657; 156148</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>152124; 193782</t>
+          <t>151189; 193962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160563; 214475</t>
+          <t>159712; 209597</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157830; 211612</t>
+          <t>159267; 210393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184530; 237516</t>
+          <t>182649; 236975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>280579; 340807</t>
+          <t>280047; 341789</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>521268; 607385</t>
+          <t>515224; 602739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>658030; 758373</t>
+          <t>654256; 752422</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>515810; 604867</t>
+          <t>517225; 610953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>524994; 747921</t>
+          <t>543491; 751662</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>774989; 873724</t>
+          <t>774864; 872861</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>925052; 1032607</t>
+          <t>927326; 1037900</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>714967; 809028</t>
+          <t>709898; 808456</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>876989; 1531163</t>
+          <t>868272; 1525198</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1317955; 1449133</t>
+          <t>1319432; 1450792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1621820; 1763894</t>
+          <t>1612201; 1764320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1244265; 1380486</t>
+          <t>1248088; 1383636</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1510829; 2255075</t>
+          <t>1509847; 2279127</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 21,75</t>
+          <t>16,87; 21,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,17; 28,56</t>
+          <t>23,16; 28,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,31</t>
+          <t>15,89; 21,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 30,01</t>
+          <t>21,15; 28,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,75; 28,71</t>
+          <t>23,54; 28,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,25; 33,26</t>
+          <t>28,15; 33,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 25,67</t>
+          <t>20,23; 25,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,71; 31,71</t>
+          <t>26,83; 31,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,33; 24,76</t>
+          <t>21,2; 24,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 30,57</t>
+          <t>26,83; 30,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,18; 23,0</t>
+          <t>18,97; 23,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,81; 29,9</t>
+          <t>25,31; 29,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,99; 18,49</t>
+          <t>15,12; 18,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 21,66</t>
+          <t>17,87; 21,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 18,62</t>
+          <t>14,95; 18,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 20,56</t>
+          <t>17,41; 21,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 25,78</t>
+          <t>21,6; 25,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 27,96</t>
+          <t>23,72; 28,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 21,6</t>
+          <t>18,04; 21,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,53; 46,62</t>
+          <t>21,68; 25,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 21,48</t>
+          <t>18,62; 21,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,14; 23,92</t>
+          <t>21,21; 23,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 19,44</t>
+          <t>17,01; 19,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,56; 34,51</t>
+          <t>19,93; 22,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 18,07</t>
+          <t>11,52; 17,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 17,91</t>
+          <t>11,25; 18,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 17,15</t>
+          <t>10,89; 17,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 25,83</t>
+          <t>19,08; 26,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 26,19</t>
+          <t>18,73; 26,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 29,63</t>
+          <t>20,67; 29,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,98; 28,57</t>
+          <t>21,19; 28,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,92; 29,41</t>
+          <t>22,97; 29,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,54; 20,39</t>
+          <t>15,73; 20,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,39</t>
+          <t>16,85; 22,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 21,71</t>
+          <t>16,92; 21,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,47; 26,2</t>
+          <t>22,05; 26,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,4</t>
+          <t>15,89; 18,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 22,02</t>
+          <t>19,18; 22,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 18,15</t>
+          <t>15,4; 18,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 21,79</t>
+          <t>19,42; 22,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,84</t>
+          <t>22,88; 25,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,11; 29,23</t>
+          <t>26,03; 29,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 22,93</t>
+          <t>20,22; 22,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,82; 41,84</t>
+          <t>23,78; 26,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 21,8</t>
+          <t>19,78; 21,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,14; 25,32</t>
+          <t>23,1; 25,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 20,07</t>
+          <t>18,15; 20,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,28; 32,12</t>
+          <t>22,05; 23,97</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132945</t>
+          <t>141516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>239669</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>381185</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>174802; 224358</t>
+          <t>174080; 224883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>225645; 278109</t>
+          <t>225554; 280307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120463; 160363</t>
+          <t>119539; 159671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115600; 154533</t>
+          <t>122359; 164179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>312365; 377621</t>
+          <t>309556; 376515</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>377691; 444573</t>
+          <t>376262; 445247</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>200823; 254620</t>
+          <t>200634; 252952</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>200727; 238325</t>
+          <t>219841; 258864</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>500576; 581056</t>
+          <t>497609; 582998</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616352; 706495</t>
+          <t>620000; 705800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>334595; 401142</t>
+          <t>330850; 403226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>326866; 378685</t>
+          <t>353867; 408330</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403857</t>
+          <t>431483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>654950</t>
+          <t>503018</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1058807</t>
+          <t>934501</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253785; 312891</t>
+          <t>255933; 319979</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348086; 424969</t>
+          <t>350649; 423058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>315050; 385356</t>
+          <t>309370; 378366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>278180; 470983</t>
+          <t>388331; 472829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>345939; 409083</t>
+          <t>342777; 408070</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>413502; 490932</t>
+          <t>416409; 494013</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>361217; 429336</t>
+          <t>358484; 431665</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>480976; 1041677</t>
+          <t>469888; 542040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>615404; 704252</t>
+          <t>610669; 708448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>785830; 889402</t>
+          <t>788377; 887763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>694716; 788659</t>
+          <t>689934; 789867</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>839755; 1561513</t>
+          <t>876545; 990043</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>190096</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>310596</t>
+          <t>349411</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63440; 99624</t>
+          <t>63532; 98745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55029; 86169</t>
+          <t>54116; 86918</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59305; 93465</t>
+          <t>59334; 93282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118497; 166598</t>
+          <t>135400; 186032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88194; 124769</t>
+          <t>89246; 125705</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97376; 135872</t>
+          <t>94797; 134821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>114657; 156148</t>
+          <t>115793; 156246</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151189; 193962</t>
+          <t>168638; 213439</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159712; 209597</t>
+          <t>161716; 213751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159267; 210393</t>
+          <t>158399; 208914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182649; 236975</t>
+          <t>184675; 238330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>280047; 341789</t>
+          <t>318359; 386680</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>676222</t>
+          <t>732314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1045094</t>
+          <t>932783</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1721316</t>
+          <t>1665098</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>515224; 602739</t>
+          <t>520496; 605763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>654256; 752422</t>
+          <t>655322; 757232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517225; 610953</t>
+          <t>518347; 607363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>543491; 751662</t>
+          <t>683276; 787739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>774864; 872861</t>
+          <t>772794; 869588</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>927326; 1037900</t>
+          <t>924395; 1032389</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>709898; 808456</t>
+          <t>713011; 804454</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>868272; 1525198</t>
+          <t>884906; 981207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1319432; 1450792</t>
+          <t>1316431; 1454107</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1612201; 1764320</t>
+          <t>1609897; 1759435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1248088; 1383636</t>
+          <t>1250995; 1386374</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1509847; 2279127</t>
+          <t>1596237; 1735347</t>
         </is>
       </c>
     </row>
